--- a/artfynd/A 42022-2025 artfynd.xlsx
+++ b/artfynd/A 42022-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339765</v>
       </c>
       <c r="B2" t="n">
-        <v>79620</v>
+        <v>79621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339766</v>
       </c>
       <c r="B3" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339762</v>
       </c>
       <c r="B4" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128339763</v>
       </c>
       <c r="B5" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128339761</v>
       </c>
       <c r="B6" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42022-2025 artfynd.xlsx
+++ b/artfynd/A 42022-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339765</v>
       </c>
       <c r="B2" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339766</v>
       </c>
       <c r="B3" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339762</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128339763</v>
       </c>
       <c r="B5" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128339761</v>
       </c>
       <c r="B6" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42022-2025 artfynd.xlsx
+++ b/artfynd/A 42022-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339765</v>
       </c>
       <c r="B2" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339766</v>
       </c>
       <c r="B3" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339762</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128339763</v>
       </c>
       <c r="B5" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128339761</v>
       </c>
       <c r="B6" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42022-2025 artfynd.xlsx
+++ b/artfynd/A 42022-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339765</v>
       </c>
       <c r="B2" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339766</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339762</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42022-2025 artfynd.xlsx
+++ b/artfynd/A 42022-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339765</v>
       </c>
       <c r="B2" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339766</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339762</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128339763</v>
       </c>
       <c r="B5" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128339761</v>
       </c>
       <c r="B6" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42022-2025 artfynd.xlsx
+++ b/artfynd/A 42022-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339765</v>
       </c>
       <c r="B2" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339766</v>
       </c>
       <c r="B3" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339762</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42022-2025 artfynd.xlsx
+++ b/artfynd/A 42022-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339765</v>
       </c>
       <c r="B2" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128339766</v>
       </c>
       <c r="B3" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128339762</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128339763</v>
       </c>
       <c r="B5" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128339761</v>
       </c>
       <c r="B6" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42022-2025 artfynd.xlsx
+++ b/artfynd/A 42022-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128339763</v>
       </c>
       <c r="B5" t="n">
-        <v>57845</v>
+        <v>57930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128339761</v>
       </c>
       <c r="B6" t="n">
-        <v>57845</v>
+        <v>57930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42022-2025 artfynd.xlsx
+++ b/artfynd/A 42022-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128339763</v>
       </c>
       <c r="B5" t="n">
-        <v>57930</v>
+        <v>57956</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128339761</v>
       </c>
       <c r="B6" t="n">
-        <v>57930</v>
+        <v>57956</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42022-2025 artfynd.xlsx
+++ b/artfynd/A 42022-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128339765</v>
+        <v>128339762</v>
       </c>
       <c r="B2" t="n">
-        <v>79714</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521022</v>
+        <v>521366</v>
       </c>
       <c r="R2" t="n">
-        <v>6846655</v>
+        <v>6846886</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -784,7 +784,7 @@
         <v>128339766</v>
       </c>
       <c r="B3" t="n">
-        <v>78881</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128339762</v>
+        <v>128339761</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>58057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521366</v>
+        <v>521164</v>
       </c>
       <c r="R4" t="n">
-        <v>6846886</v>
+        <v>6846905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,11 +996,11 @@
         <v>128339763</v>
       </c>
       <c r="B5" t="n">
-        <v>57956</v>
+        <v>58057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339761</v>
+        <v>128339765</v>
       </c>
       <c r="B6" t="n">
-        <v>57956</v>
+        <v>79917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521164</v>
+        <v>521022</v>
       </c>
       <c r="R6" t="n">
-        <v>6846905</v>
+        <v>6846655</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 42022-2025 artfynd.xlsx
+++ b/artfynd/A 42022-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339762</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339766</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339761</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339763</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339765</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>